--- a/documentos/Cronograma_semanal Proyecto  (1).xlsx
+++ b/documentos/Cronograma_semanal Proyecto  (1).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENA\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40DA695-E534-4DE6-A981-1E486D76DB21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8517A9D2-D3D5-406E-94B0-9ACE0D747EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7035" yWindow="750" windowWidth="15615" windowHeight="14730" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cronograma semanal" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t>CRONOGRAMA SEMANAL DE ACTIVIDADES</t>
   </si>
@@ -132,12 +132,6 @@
     <t>12:00pm-6:00pm</t>
   </si>
   <si>
-    <t>Se realizó el diseño de las interfaces de el admin</t>
-  </si>
-  <si>
-    <t>Se agregó un diagrama de casos de uso que faltaba</t>
-  </si>
-  <si>
     <t>ADSO</t>
   </si>
   <si>
@@ -147,31 +141,19 @@
     <t>Dizar Asociados</t>
   </si>
   <si>
-    <t xml:space="preserve">Se cambiaron las opciones que aparecen al tocar el inconó en la parte superior derecha, agregando animaciones </t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Se arregló el diseño del inicio de sesion y del inico</t>
-  </si>
-  <si>
-    <t>Se agregó un nuevo apartado de opiniones en el cual los clientes dan opiniones sobre los abogados</t>
-  </si>
-  <si>
-    <t>se le añadió un diseño a la nueva dashboard</t>
-  </si>
-  <si>
-    <t>se agregaron nuevos apartado de entre los cuales está la dashboard de los abogados</t>
-  </si>
-  <si>
-    <t>Se agregó un nuevo botón en el inicio de sesion</t>
-  </si>
-  <si>
-    <t>se le dió un buen diseño al nuevo boton</t>
-  </si>
-  <si>
-    <t>se le añadió un diseño a la nueva dashboard y se mejoró el diseño del boton</t>
+    <t>Se agregó un apartado para los casos, notificaciones, caso, subir documentos, el seguimiento y el chat.</t>
+  </si>
+  <si>
+    <t>Se rediseñó la interfáz de casos, chat y documentos</t>
+  </si>
+  <si>
+    <t>nuevo diseño del digrama de casos de uso</t>
+  </si>
+  <si>
+    <t>está en proceso el cambio de php a python</t>
   </si>
 </sst>
 </file>
@@ -709,7 +691,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -717,7 +699,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="2">
-        <v>46314</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -725,7 +707,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" s="16"/>
       <c r="D4" s="16"/>
@@ -734,7 +716,7 @@
       </c>
       <c r="G4" s="3">
         <f>G3+4</f>
-        <v>46318</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -742,7 +724,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
@@ -793,23 +775,23 @@
       <c r="B9" s="5"/>
       <c r="C9" s="6">
         <f>$G$3+0</f>
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="D9" s="6">
         <f>$G$3+1</f>
-        <v>46315</v>
+        <v>46322</v>
       </c>
       <c r="E9" s="6">
         <f>$G$3+2</f>
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="F9" s="6">
         <f>$G$3+3</f>
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="G9" s="6">
         <f>$G$3+4</f>
-        <v>46318</v>
+        <v>46325</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6" t="s">
@@ -824,20 +806,16 @@
         <v>22</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>36</v>
-      </c>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
     </row>
@@ -849,20 +827,16 @@
         <v>22</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>33</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
     </row>
@@ -874,20 +848,16 @@
         <v>22</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
     </row>
